--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T07:40:29+00:00</t>
+    <t>2026-08-24T13:49:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:49:26+00:00</t>
+    <t>2026-08-28T09:59:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:59:02+00:00</t>
+    <t>2026-08-28T10:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:19:24+00:00</t>
+    <t>2026-09-01T07:28:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T07:28:55+00:00</t>
+    <t>2026-09-01T08:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:17:52+00:00</t>
+    <t>2026-09-01T11:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:26:20+00:00</t>
+    <t>2026-09-01T11:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:37:07+00:00</t>
+    <t>2026-09-01T11:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:44:40+00:00</t>
+    <t>2026-09-01T12:05:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:05:15+00:00</t>
+    <t>2026-09-01T12:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:12:27+00:00</t>
+    <t>2026-09-01T12:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:31:59+00:00</t>
+    <t>2026-09-01T12:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:37:11+00:00</t>
+    <t>2026-09-01T12:41:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:41:57+00:00</t>
+    <t>2026-09-01T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:58:26+00:00</t>
+    <t>2026-09-01T13:38:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:38:20+00:00</t>
+    <t>2026-09-01T13:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,13 +105,13 @@
     <t>399445004</t>
   </si>
   <si>
-    <t>Specimen collection date (observable entity)</t>
+    <t>Specimen collection date</t>
   </si>
   <si>
     <t>281271004</t>
   </si>
   <si>
-    <t>Date sample received in laboratory (observable entity)</t>
+    <t>Date sample received in laboratory</t>
   </si>
   <si>
     <t/>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:44:38+00:00</t>
+    <t>2026-09-01T14:35:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:35:41+00:00</t>
+    <t>2026-09-01T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:11:46+00:00</t>
+    <t>2026-09-01T15:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:27:37+00:00</t>
+    <t>2026-09-01T15:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:32:49+00:00</t>
+    <t>2026-09-01T15:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:38:53+00:00</t>
+    <t>2026-09-01T16:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:17:13+00:00</t>
+    <t>2026-09-01T16:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:23:29+00:00</t>
+    <t>2026-09-02T06:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:57:39+00:00</t>
+    <t>2026-09-02T07:24:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:24:40+00:00</t>
+    <t>2026-09-02T08:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T08:07:59+00:00</t>
+    <t>2026-09-02T09:10:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:10:52+00:00</t>
+    <t>2026-09-02T09:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:21:54+00:00</t>
+    <t>2026-09-02T10:32:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:32:32+00:00</t>
+    <t>2026-09-02T10:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:47:13+00:00</t>
+    <t>2026-09-02T11:41:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/ValueSet-mii-vs-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T11:41:16+00:00</t>
+    <t>2026-09-02T11:51:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
